--- a/countries/br-df/2026-2029.xlsx
+++ b/countries/br-df/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5195,6 +5330,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5331,6 +5471,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5467,6 +5612,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5603,6 +5753,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5739,6 +5894,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6250,6 +6410,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6386,6 +6551,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6522,6 +6692,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6658,6 +6833,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6794,6 +6974,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6930,6 +7115,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7066,6 +7256,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7202,6 +7397,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7338,6 +7538,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7474,6 +7679,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7610,6 +7820,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7746,6 +7961,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7882,6 +8102,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8018,6 +8243,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8154,6 +8384,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8290,6 +8525,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8426,6 +8666,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8562,6 +8807,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8698,6 +8948,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8834,6 +9089,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8970,6 +9230,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9106,6 +9371,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9242,6 +9512,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9378,6 +9653,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9514,6 +9794,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9650,6 +9935,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9786,6 +10076,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10672,6 +10967,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10808,6 +11108,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10944,6 +11249,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11080,6 +11390,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11591,6 +11906,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12102,6 +12422,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12238,6 +12563,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12374,6 +12704,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12510,6 +12845,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12782,6 +13122,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12918,6 +13263,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13054,6 +13404,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13190,6 +13545,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13326,6 +13686,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13462,6 +13827,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13598,6 +13968,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13734,6 +14109,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13870,6 +14250,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14006,6 +14391,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14142,6 +14532,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14278,6 +14673,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14414,6 +14814,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14550,6 +14955,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14686,6 +15096,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14822,6 +15237,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14958,6 +15378,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15094,6 +15519,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15230,6 +15660,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15366,6 +15801,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15502,6 +15942,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16388,6 +16833,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16524,6 +16974,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16660,6 +17115,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17171,6 +17631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17682,6 +18147,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17818,6 +18288,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17954,6 +18429,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18090,6 +18570,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18226,6 +18711,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18362,6 +18852,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18498,6 +18993,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18634,6 +19134,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18770,6 +19275,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18906,6 +19416,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19042,6 +19557,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19178,6 +19698,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19314,6 +19839,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19450,6 +19980,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19586,6 +20121,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19722,6 +20262,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19858,6 +20403,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19994,6 +20544,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20130,6 +20685,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20266,6 +20826,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20402,6 +20967,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20538,6 +21108,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20674,6 +21249,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20810,6 +21390,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20946,6 +21531,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21082,6 +21672,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21968,6 +22563,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22104,6 +22704,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22240,6 +22845,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22751,6 +23361,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23262,6 +23877,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23398,6 +24018,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23534,6 +24159,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23670,6 +24300,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23806,6 +24441,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23942,6 +24582,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24078,6 +24723,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24214,6 +24864,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24350,6 +25005,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24486,6 +25146,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24622,6 +25287,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24758,6 +25428,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24894,6 +25569,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25030,6 +25710,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25166,6 +25851,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25302,6 +25992,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25438,6 +26133,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25574,6 +26274,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25710,6 +26415,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25846,6 +26556,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25982,6 +26697,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26118,6 +26838,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27004,6 +27729,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27140,6 +27870,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27651,6 +28386,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28162,6 +28902,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28298,6 +29043,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28434,6 +29184,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28570,6 +29325,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28706,6 +29466,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28842,6 +29607,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28978,6 +29748,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29114,6 +29889,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29250,6 +30030,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29386,6 +30171,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29522,6 +30312,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29658,6 +30453,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29794,6 +30594,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29930,6 +30735,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30066,6 +30876,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30202,6 +31017,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30338,6 +31158,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30474,6 +31299,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31360,6 +32190,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31496,6 +32331,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31632,6 +32472,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32143,6 +32988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32279,6 +33129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32415,6 +33270,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32551,6 +33411,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32687,6 +33552,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32823,6 +33693,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32959,6 +33834,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33095,6 +33975,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33231,6 +34116,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33367,6 +34257,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33503,6 +34398,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33639,6 +34539,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33775,6 +34680,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33911,6 +34821,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34047,6 +34962,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34183,6 +35103,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34319,6 +35244,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35205,6 +36135,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35341,6 +36276,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35477,6 +36417,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35988,6 +36933,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36124,6 +37074,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36260,6 +37215,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36396,6 +37356,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36532,6 +37497,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36668,6 +37638,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36804,6 +37779,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36940,6 +37920,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37076,6 +38061,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37212,6 +38202,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37348,6 +38343,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37484,6 +38484,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37620,6 +38625,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37756,6 +38766,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37892,6 +38907,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38778,6 +39798,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38914,6 +39939,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39050,6 +40080,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39561,6 +40596,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39697,6 +40737,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39833,6 +40878,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39969,6 +41019,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40105,6 +41160,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40241,6 +41301,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40377,6 +41442,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40513,6 +41583,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40649,6 +41724,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40785,6 +41865,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40921,6 +42006,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41055,6 +42145,11 @@
       <c r="S277" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">

--- a/countries/br-df/2026-2029.xlsx
+++ b/countries/br-df/2026-2029.xlsx
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16302,7 +16302,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -17475,7 +17475,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22032,7 +22032,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -27198,7 +27198,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -27573,7 +27573,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -32034,7 +32034,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -35604,7 +35604,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -39267,7 +39267,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -39642,7 +39642,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">

--- a/countries/br-df/2026-2029.xlsx
+++ b/countries/br-df/2026-2029.xlsx
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="O3" t="n">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="R3" t="n">
-        <v>13.18938629818777</v>
+        <v>12.85715994306969</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -6538,13 +6538,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="O41" t="n">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="R41" t="n">
-        <v>12.29237513936896</v>
+        <v>11.59469979362099</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -12409,13 +12409,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>666</v>
+        <v>593</v>
       </c>
       <c r="O80" t="n">
-        <v>666</v>
+        <v>593</v>
       </c>
       <c r="R80" t="n">
-        <v>22.12627525086412</v>
+        <v>19.70102285850214</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -18275,13 +18275,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>653</v>
+        <v>621</v>
       </c>
       <c r="O119" t="n">
-        <v>653</v>
+        <v>621</v>
       </c>
       <c r="R119" t="n">
-        <v>21.69438098921062</v>
+        <v>20.63125665283276</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20531,13 +20531,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="O156" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="R156" t="n">
-        <v>13.88706164393574</v>
+        <v>13.68772583086489</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -25809,22 +25809,22 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D168</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>先天性风疹综合征</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -25950,17 +25950,17 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>D184</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Accident caused by venomous animals</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>毒性动物伤害</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -25979,13 +25979,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>14.85051807377817</v>
+        <v>0</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -26091,17 +26091,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>D185</t>
+          <t>D184</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Work accident with biological material</t>
+          <t>Accident caused by venomous animals</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>生物材料职业暴露事故</t>
+          <t>毒性动物伤害</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -26120,13 +26120,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>185</v>
+        <v>447</v>
       </c>
       <c r="O172" t="n">
-        <v>185</v>
+        <v>447</v>
       </c>
       <c r="R172" t="n">
-        <v>6.146187569684478</v>
+        <v>14.85051807377817</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -26232,17 +26232,17 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>D186</t>
+          <t>D185</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Serious work accident</t>
+          <t>Work accident with biological material</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>严重工伤</t>
+          <t>生物材料职业暴露事故</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -26261,13 +26261,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>959</v>
+        <v>185</v>
       </c>
       <c r="O173" t="n">
-        <v>959</v>
+        <v>185</v>
       </c>
       <c r="R173" t="n">
-        <v>31.86050745582386</v>
+        <v>6.146187569684478</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -26373,17 +26373,17 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>D187</t>
+          <t>D186</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Rabies post-exposure prophylaxis</t>
+          <t>Serious work accident</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>狂犬病暴露后处置</t>
+          <t>严重工伤</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -26402,13 +26402,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>711</v>
+        <v>959</v>
       </c>
       <c r="O174" t="n">
-        <v>711</v>
+        <v>959</v>
       </c>
       <c r="R174" t="n">
-        <v>23.62129384889548</v>
+        <v>31.86050745582386</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -26514,17 +26514,17 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>D188</t>
+          <t>D187</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>Rabies post-exposure prophylaxis</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>职业相关癌症</t>
+          <t>狂犬病暴露后处置</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -26543,13 +26543,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="O175" t="n">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>23.62129384889548</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -26655,17 +26655,17 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>D189</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Work-related dermatosis</t>
+          <t>Work-related cancer</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>职业性皮肤病</t>
+          <t>职业相关癌症</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -26796,17 +26796,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D189</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Work-related dermatosis</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>职业性皮肤病</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -26825,13 +26825,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>33.22263551180799</v>
+        <v>0</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -26937,17 +26937,17 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D191</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Exogenous poisoning</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>外源性中毒</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -26966,24 +26966,19 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>138</v>
+        <v>1000</v>
       </c>
       <c r="O178" t="n">
-        <v>138</v>
+        <v>1000</v>
       </c>
       <c r="R178" t="n">
-        <v>4.584723700629502</v>
+        <v>33.22263551180799</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26991,30 +26986,26 @@
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -27072,7 +27063,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -27121,98 +27112,23 @@
       <c r="O179" t="n">
         <v>138</v>
       </c>
+      <c r="R179" t="n">
+        <v>4.584723700629502</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_BR_LERD</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Work-related repetitive strain injury</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -27297,7 +27213,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -27312,17 +27228,17 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -27341,22 +27257,39 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="O180" t="n">
-        <v>14</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.4651168971653118</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
+        <v>138</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -27364,6 +27297,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>1</v>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27381,7 +27372,7 @@
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="AT180" t="n">
@@ -27447,7 +27438,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -27496,98 +27487,23 @@
       <c r="O181" t="n">
         <v>14</v>
       </c>
+      <c r="R181" t="n">
+        <v>0.4651168971653118</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>SER_BR_WORK_MENTAL_MENT</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Work-related mental disorder</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>SINAN MENT work-related mental disorder notifications.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -27672,7 +27588,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -27687,17 +27603,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>D194</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Noise-induced hearing loss</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>噪声性听力损失</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -27716,17 +27632,39 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>14</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Work-related mental disorder</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -27734,28 +27672,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>SINAN MENT work-related mental disorder notifications.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -27828,17 +27828,17 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>D195</t>
+          <t>D194</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Pneumoconiosis</t>
+          <t>Noise-induced hearing loss</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>尘肺病</t>
+          <t>噪声性听力损失</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -27969,22 +27969,22 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>D200</t>
+          <t>D195</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Trachoma</t>
+          <t>Pneumoconiosis</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>沙眼</t>
+          <t>尘肺病</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -28011,11 +28011,6 @@
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_BR_TRACHOMA_CASE_TRAC</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28023,30 +28018,26 @@
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_BR_TRACHOMA_CASE_TRAC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -28104,7 +28095,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -28153,98 +28144,23 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>SER_BR_TRACHOMA_CASE_TRAC</t>
         </is>
       </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_BR_TRACHOMA_CASE_TRAC</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Trachoma</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>SINAN TRAC individual trachoma notification family.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -28329,7 +28245,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -28344,22 +28260,22 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D200</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Trachoma</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>沙眼</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -28373,17 +28289,39 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>3</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0.09966790653542397</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_BR_TRACHOMA_CASE_TRAC</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_BR_TRACHOMA_CASE_TRAC</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Trachoma</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -28391,28 +28329,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>SINAN TRAC individual trachoma notification family.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_BR_TRACHOMA_CASE_TRAC</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -28485,22 +28485,22 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D201</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Exanthematous diseases</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>出疹性疾病</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -28514,24 +28514,19 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O187" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="R187" t="n">
-        <v>0.4983395326771199</v>
+        <v>0.09966790653542397</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28539,30 +28534,26 @@
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -28620,7 +28611,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -28669,98 +28660,23 @@
       <c r="O188" t="n">
         <v>15</v>
       </c>
+      <c r="R188" t="n">
+        <v>0.4983395326771199</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
         </is>
       </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Meningitis</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>reported_aggregate</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>BR_SINAN_MENI_current</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN188" t="b">
-        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
@@ -28845,7 +28761,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -28860,46 +28776,68 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N189" t="n">
-        <v>419</v>
+        <v>15</v>
       </c>
       <c r="O189" t="n">
-        <v>419</v>
-      </c>
-      <c r="R189" t="n">
-        <v>13.92028427944755</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>15</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -28907,28 +28845,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
+        <v>1</v>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -29001,22 +29001,22 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -29030,13 +29030,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>4</v>
+        <v>418</v>
       </c>
       <c r="O190" t="n">
-        <v>4</v>
+        <v>418</v>
       </c>
       <c r="R190" t="n">
-        <v>0.132890542047232</v>
+        <v>13.88706164393574</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -29142,17 +29142,17 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -29171,13 +29171,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>0.132890542047232</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -29283,17 +29283,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -29312,13 +29312,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>0.2990037196062719</v>
+        <v>0</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -29424,22 +29424,22 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -29453,13 +29453,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O193" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R193" t="n">
-        <v>0.1661131775590399</v>
+        <v>0.2990037196062719</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -29565,22 +29565,22 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>D042</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Leprosy</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>麻风病</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -29594,13 +29594,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O194" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R194" t="n">
-        <v>0.3986716261416959</v>
+        <v>0.1661131775590399</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -29706,22 +29706,22 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>D051</t>
+          <t>D042</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Zika virus disease</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>寨卡病毒病</t>
+          <t>麻风病</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -29735,13 +29735,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O195" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R195" t="n">
-        <v>0.06644527102361598</v>
+        <v>0.3986716261416959</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -29847,17 +29847,17 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D051</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Zika virus disease</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>寨卡病毒病</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -29876,13 +29876,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="O196" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="R196" t="n">
-        <v>1.727577046614015</v>
+        <v>0.06644527102361598</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -29988,17 +29988,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -30017,13 +30017,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="O197" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="R197" t="n">
-        <v>0.7641206167715837</v>
+        <v>1.694354411102207</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -30129,22 +30129,22 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>D118</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Spotted fever rickettsiosis</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>斑点热立克次体病</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -30158,13 +30158,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="O198" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="R198" t="n">
-        <v>0.2657810840944639</v>
+        <v>0.7641206167715837</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -30270,17 +30270,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D118</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Spotted fever rickettsiosis</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>斑点热立克次体病</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -30299,13 +30299,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O199" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R199" t="n">
-        <v>0.03322263551180799</v>
+        <v>0.2657810840944639</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -30411,22 +30411,22 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -30440,13 +30440,13 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -30552,22 +30552,22 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>D184</t>
+          <t>D168</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Accident caused by venomous animals</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>毒性动物伤害</t>
+          <t>先天性风疹综合征</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -30581,13 +30581,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>13.62128055984127</v>
+        <v>0</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -30693,17 +30693,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>D185</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Work accident with biological material</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>生物材料职业暴露事故</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -30722,13 +30722,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>4.551501065117694</v>
+        <v>0</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -30834,17 +30834,17 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>D186</t>
+          <t>D184</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Serious work accident</t>
+          <t>Accident caused by venomous animals</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>严重工伤</t>
+          <t>毒性动物伤害</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -30863,13 +30863,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>823</v>
+        <v>410</v>
       </c>
       <c r="O203" t="n">
-        <v>823</v>
+        <v>410</v>
       </c>
       <c r="R203" t="n">
-        <v>27.34222902621798</v>
+        <v>13.62128055984127</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -30975,17 +30975,17 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>D188</t>
+          <t>D185</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>Work accident with biological material</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>职业相关癌症</t>
+          <t>生物材料职业暴露事故</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>4.551501065117694</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -31116,17 +31116,17 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>D189</t>
+          <t>D186</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Work-related dermatosis</t>
+          <t>Serious work accident</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>职业性皮肤病</t>
+          <t>严重工伤</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -31145,13 +31145,13 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>27.34222902621798</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -31257,17 +31257,17 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Work-related cancer</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>职业相关癌症</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -31286,13 +31286,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>32.95685442771353</v>
+        <v>0</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -31398,17 +31398,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D189</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Work-related dermatosis</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>职业性皮肤病</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -31427,24 +31427,19 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>4.551501065117694</v>
+        <v>0</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31452,30 +31447,26 @@
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -31533,7 +31524,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -31548,17 +31539,17 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D191</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Exogenous poisoning</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>外源性中毒</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -31577,39 +31568,17 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>137</v>
+        <v>992</v>
       </c>
       <c r="O208" t="n">
-        <v>137</v>
-      </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Work-related repetitive strain injury</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>992</v>
+      </c>
+      <c r="R208" t="n">
+        <v>32.95685442771353</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -31617,90 +31586,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
-      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -31773,17 +31680,17 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -31802,13 +31709,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="O209" t="n">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="R209" t="n">
-        <v>0.6312300747243518</v>
+        <v>4.551501065117694</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -31817,7 +31724,7 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -31842,7 +31749,7 @@
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="AT209" t="n">
@@ -31923,17 +31830,17 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -31952,19 +31859,19 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="O210" t="n">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
@@ -31974,7 +31881,7 @@
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -32039,7 +31946,7 @@
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>SINAN MENT work-related mental disorder notifications.</t>
+          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
@@ -32067,7 +31974,7 @@
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="AT210" t="n">
@@ -32148,17 +32055,17 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>D194</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Noise-induced hearing loss</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>噪声性听力损失</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -32177,19 +32084,24 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>0.6312300747243518</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32197,26 +32109,30 @@
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -32274,7 +32190,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -32289,17 +32205,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>D195</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Pneumoconiosis</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>尘肺病</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -32318,17 +32234,39 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>19</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Work-related mental disorder</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -32336,28 +32274,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>SINAN MENT work-related mental disorder notifications.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
@@ -32430,22 +32430,22 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D194</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Noise-induced hearing loss</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>噪声性听力损失</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -32459,13 +32459,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>0.06644527102361598</v>
+        <v>0</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -32571,17 +32571,17 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D195</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Pneumoconiosis</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>尘肺病</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -32600,24 +32600,19 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>0.5315621681889279</v>
+        <v>0</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32625,30 +32620,26 @@
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ214" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -32706,7 +32697,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -32721,22 +32712,22 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D201</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Exanthematous diseases</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>出疹性疾病</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -32750,39 +32741,17 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O215" t="n">
-        <v>16</v>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>Meningitis</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>2</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0.06644527102361598</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -32790,90 +32759,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>reported_aggregate</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>BR_SINAN_MENI_current</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN215" t="b">
-        <v>1</v>
-      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -32946,48 +32853,53 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>324</v>
+        <v>16</v>
       </c>
       <c r="O216" t="n">
-        <v>324</v>
+        <v>16</v>
       </c>
       <c r="R216" t="n">
-        <v>10.76413390582579</v>
+        <v>0.5315621681889279</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32995,26 +32907,30 @@
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AT216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -33072,7 +32988,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -33087,46 +33003,68 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N217" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O217" t="n">
-        <v>6</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0.1993358130708479</v>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>16</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -33134,28 +33072,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -33228,22 +33228,22 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -33257,13 +33257,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>10.73091127031398</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -33369,17 +33369,17 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>0.1993358130708479</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -33510,17 +33510,17 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>D042</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Leprosy</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>麻风病</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -33539,13 +33539,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>0.6312300747243518</v>
+        <v>0</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -33651,22 +33651,22 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>D051</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Zika virus disease</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>寨卡病毒病</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -33680,13 +33680,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0.03322263551180799</v>
+        <v>0</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -33792,22 +33792,22 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D042</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>麻风病</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -33821,13 +33821,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="O222" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="R222" t="n">
-        <v>1.827244953149439</v>
+        <v>0.6312300747243518</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -33933,17 +33933,17 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D051</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Zika virus disease</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>寨卡病毒病</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -33962,13 +33962,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R223" t="n">
-        <v>0.5315621681889279</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -34074,22 +34074,22 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>D118</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Spotted fever rickettsiosis</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>斑点热立克次体病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -34103,13 +34103,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="O224" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>1.760799682125823</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -34215,22 +34215,22 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -34244,13 +34244,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>0.5315621681889279</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -34356,22 +34356,22 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D118</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Spotted fever rickettsiosis</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>斑点热立克次体病</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -34497,22 +34497,22 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>D184</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Accident caused by venomous animals</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>毒性动物伤害</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -34526,13 +34526,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>13.38872211125862</v>
+        <v>0</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -34638,22 +34638,22 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D185</t>
+          <t>D168</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Work accident with biological material</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>生物材料职业暴露事故</t>
+          <t>先天性风疹综合征</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -34667,13 +34667,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>5.083063233306622</v>
+        <v>0</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -34779,17 +34779,17 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>D186</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Serious work accident</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>严重工伤</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -34808,13 +34808,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>954</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>954</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>31.69439427826482</v>
+        <v>0</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -34920,17 +34920,17 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>D188</t>
+          <t>D184</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>Accident caused by venomous animals</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>职业相关癌症</t>
+          <t>毒性动物伤害</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -34949,13 +34949,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="O230" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>13.38872211125862</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -35061,17 +35061,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D189</t>
+          <t>D185</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Work-related dermatosis</t>
+          <t>Work accident with biological material</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>职业性皮肤病</t>
+          <t>生物材料职业暴露事故</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -35090,13 +35090,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>5.083063233306622</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -35202,17 +35202,17 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D186</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Serious work accident</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>严重工伤</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -35231,13 +35231,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1149</v>
+        <v>954</v>
       </c>
       <c r="O232" t="n">
-        <v>1149</v>
+        <v>954</v>
       </c>
       <c r="R232" t="n">
-        <v>38.17280820306738</v>
+        <v>31.69439427826482</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -35343,17 +35343,17 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Work-related cancer</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>职业相关癌症</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -35372,24 +35372,19 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>4.186052074487807</v>
+        <v>0</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35397,30 +35392,26 @@
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -35478,7 +35469,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -35493,17 +35484,17 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D189</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Work-related dermatosis</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>职业性皮肤病</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -35522,39 +35513,17 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
-        <v>126</v>
-      </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>Work-related repetitive strain injury</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -35562,90 +35531,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD234" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE234" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG234" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ234" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK234" t="inlineStr">
-        <is>
-          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
-        </is>
-      </c>
-      <c r="AM234" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN234" t="b">
-        <v>1</v>
-      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -35718,17 +35625,17 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D191</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Exogenous poisoning</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>外源性中毒</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -35747,24 +35654,19 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>12</v>
+        <v>1149</v>
       </c>
       <c r="O235" t="n">
-        <v>12</v>
+        <v>1149</v>
       </c>
       <c r="R235" t="n">
-        <v>0.3986716261416959</v>
+        <v>38.17280820306738</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35772,30 +35674,26 @@
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -35853,7 +35751,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -35868,17 +35766,17 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -35897,39 +35795,22 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="O236" t="n">
-        <v>12</v>
+        <v>126</v>
+      </c>
+      <c r="R236" t="n">
+        <v>4.186052074487807</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
-      <c r="W236" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X236" t="inlineStr">
-        <is>
-          <t>Work-related mental disorder</t>
-        </is>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -35937,64 +35818,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD236" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE236" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG236" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>SINAN MENT work-related mental disorder notifications.</t>
-        </is>
-      </c>
-      <c r="AM236" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN236" t="b">
-        <v>1</v>
-      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36012,7 +35835,7 @@
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="AT236" t="n">
@@ -36078,7 +35901,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -36093,17 +35916,17 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D194</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Noise-induced hearing loss</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>噪声性听力损失</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -36122,17 +35945,39 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="O237" t="n">
-        <v>0</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0</v>
-      </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>126</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -36140,28 +35985,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN237" t="b">
+        <v>1</v>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
       <c r="AT237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
@@ -36234,17 +36141,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>D195</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Pneumoconiosis</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>尘肺病</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -36263,19 +36170,24 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>0.3986716261416959</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36283,26 +36195,30 @@
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS238" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ238" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
@@ -36360,7 +36276,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -36375,22 +36291,22 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -36404,46 +36320,130 @@
         </is>
       </c>
       <c r="N239" t="n">
+        <v>12</v>
+      </c>
+      <c r="O239" t="n">
+        <v>12</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Work-related mental disorder</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>SINAN MENT work-related mental disorder notifications.</t>
+        </is>
+      </c>
+      <c r="AM239" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN239" t="b">
         <v>1</v>
       </c>
-      <c r="O239" t="n">
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="AT239" t="n">
         <v>1</v>
       </c>
-      <c r="R239" t="n">
-        <v>0.03322263551180799</v>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP239" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
-      <c r="AT239" t="n">
-        <v>0</v>
-      </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -36516,17 +36516,17 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D194</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Noise-induced hearing loss</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>噪声性听力损失</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -36545,24 +36545,19 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>1.129569607401472</v>
+        <v>0</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36570,30 +36565,26 @@
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -36651,7 +36642,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -36666,17 +36657,17 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D195</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Pneumoconiosis</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>尘肺病</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -36695,39 +36686,17 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
-        <v>34</v>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>Meningitis</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -36735,90 +36704,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>reported_aggregate</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>BR_SINAN_MENI_current</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN241" t="b">
-        <v>1</v>
-      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -36891,17 +36798,17 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D201</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Exanthematous diseases</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>出疹性疾病</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -36911,22 +36818,22 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N242" t="n">
-        <v>322</v>
+        <v>1</v>
       </c>
       <c r="O242" t="n">
-        <v>322</v>
+        <v>1</v>
       </c>
       <c r="R242" t="n">
-        <v>10.69768863480217</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -37032,75 +36939,84 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N243" t="n">
+        <v>34</v>
+      </c>
+      <c r="O243" t="n">
+        <v>34</v>
+      </c>
+      <c r="R243" t="n">
+        <v>1.129569607401472</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT243" t="n">
         <v>1</v>
       </c>
-      <c r="O243" t="n">
-        <v>1</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0.03322263551180799</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO243" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP243" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS243" t="inlineStr"/>
-      <c r="AT243" t="n">
-        <v>0</v>
-      </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
@@ -37158,7 +37074,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -37173,46 +37089,68 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>34</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -37220,28 +37158,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
@@ -37314,22 +37314,22 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>D042</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Leprosy</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>麻风病</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -37343,13 +37343,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>17</v>
+        <v>291</v>
       </c>
       <c r="O245" t="n">
-        <v>17</v>
+        <v>291</v>
       </c>
       <c r="R245" t="n">
-        <v>0.5647848037007358</v>
+        <v>9.667786933936124</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -37455,22 +37455,22 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>D051</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Zika virus disease</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>寨卡病毒病</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -37596,22 +37596,22 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -37625,13 +37625,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>1.528241233543167</v>
+        <v>0</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -37737,22 +37737,22 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D042</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>麻风病</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -37878,22 +37878,22 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D051</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Zika virus disease</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>寨卡病毒病</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -37907,13 +37907,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -38019,22 +38019,22 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -38048,13 +38048,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>1.49501859803136</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -38160,22 +38160,22 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>D184</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Accident caused by venomous animals</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>毒性动物伤害</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -38189,13 +38189,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>425</v>
+        <v>17</v>
       </c>
       <c r="O251" t="n">
-        <v>425</v>
+        <v>17</v>
       </c>
       <c r="R251" t="n">
-        <v>14.11962009251839</v>
+        <v>0.5647848037007358</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -38301,22 +38301,22 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>D185</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Work accident with biological material</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>生物材料职业暴露事故</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -38330,13 +38330,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>3.156150373621759</v>
+        <v>0</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -38442,22 +38442,22 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>D186</t>
+          <t>D168</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Serious work accident</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>严重工伤</t>
+          <t>先天性风疹综合征</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -38471,13 +38471,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>17.50832891472281</v>
+        <v>0</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -38583,17 +38583,17 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>D188</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>职业相关癌症</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -38724,17 +38724,17 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>D189</t>
+          <t>D184</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Work-related dermatosis</t>
+          <t>Accident caused by venomous animals</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>职业性皮肤病</t>
+          <t>毒性动物伤害</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -38753,13 +38753,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="O255" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>14.11962009251839</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -38865,17 +38865,17 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D185</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Work accident with biological material</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>生物材料职业暴露事故</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -38894,13 +38894,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>1244</v>
+        <v>95</v>
       </c>
       <c r="O256" t="n">
-        <v>1244</v>
+        <v>95</v>
       </c>
       <c r="R256" t="n">
-        <v>41.32895857668914</v>
+        <v>3.156150373621759</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -39006,17 +39006,17 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D186</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Serious work accident</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>严重工伤</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -39035,24 +39035,19 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>106</v>
+        <v>527</v>
       </c>
       <c r="O257" t="n">
-        <v>106</v>
+        <v>527</v>
       </c>
       <c r="R257" t="n">
-        <v>3.521599364251647</v>
+        <v>17.50832891472281</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39060,30 +39055,26 @@
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
@@ -39141,7 +39132,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -39156,17 +39147,17 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Work-related cancer</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>职业相关癌症</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -39185,39 +39176,17 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>106</v>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>Work-related repetitive strain injury</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -39225,90 +39194,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN258" t="b">
-        <v>1</v>
-      </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
@@ -39381,17 +39288,17 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D189</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Work-related dermatosis</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>职业性皮肤病</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -39410,24 +39317,19 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>0.4318942616535039</v>
+        <v>0</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39435,30 +39337,26 @@
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
@@ -39516,7 +39414,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -39531,17 +39429,17 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D191</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Exogenous poisoning</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>外源性中毒</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -39560,39 +39458,17 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>13</v>
+        <v>1244</v>
       </c>
       <c r="O260" t="n">
-        <v>13</v>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>Work-related mental disorder</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>1244</v>
+      </c>
+      <c r="R260" t="n">
+        <v>41.32895857668914</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -39600,90 +39476,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>SINAN MENT work-related mental disorder notifications.</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN260" t="b">
-        <v>1</v>
-      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ260" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
@@ -39756,17 +39570,17 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>D194</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Noise-induced hearing loss</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>噪声性听力损失</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -39785,19 +39599,24 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>3.521599364251647</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39805,26 +39624,30 @@
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -39882,7 +39705,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -39897,17 +39720,17 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>D195</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Pneumoconiosis</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>尘肺病</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -39926,17 +39749,39 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0</v>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>106</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>Work-related repetitive strain injury</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -39944,28 +39789,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>SINAN LERD work-related repetitive strain injury or musculoskeletal disorder notifications; LER is retained as the historical source code alias.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
@@ -40038,22 +39945,22 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -40067,19 +39974,24 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O263" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R263" t="n">
-        <v>0.132890542047232</v>
+        <v>0.4318942616535039</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40087,26 +39999,30 @@
       </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
@@ -40164,7 +40080,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -40179,17 +40095,17 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -40208,22 +40124,39 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O264" t="n">
-        <v>19</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0.6312300747243518</v>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Work-related mental disorder</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -40231,6 +40164,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>SINAN MENT work-related mental disorder notifications.</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN264" t="b">
+        <v>1</v>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40248,7 +40239,7 @@
       </c>
       <c r="AS264" t="inlineStr">
         <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
         </is>
       </c>
       <c r="AT264" t="n">
@@ -40314,7 +40305,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -40329,17 +40320,17 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D194</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Noise-induced hearing loss</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>噪声性听力损失</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -40358,39 +40349,17 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>19</v>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>Meningitis</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -40398,90 +40367,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>reported_aggregate</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>BR_SINAN_MENI_current</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN265" t="b">
-        <v>1</v>
-      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -40554,42 +40461,42 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D195</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Pneumoconiosis</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>尘肺病</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N266" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>16.04653295220326</v>
+        <v>0</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -40695,42 +40602,42 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D201</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Exanthematous diseases</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>出疹性疾病</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R267" t="n">
-        <v>0.03322263551180799</v>
+        <v>0.132890542047232</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -40836,48 +40743,53 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O268" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>0.6312300747243518</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40885,26 +40797,30 @@
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
@@ -40962,7 +40878,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -40977,46 +40893,68 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>D042</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Leprosy</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>麻风病</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+        <v>19</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -41024,28 +40962,90 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
@@ -41118,17 +41118,17 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>D051</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Zika virus disease</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>寨卡病毒病</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -41147,13 +41147,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="O270" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="R270" t="n">
-        <v>0</v>
+        <v>15.21596706440806</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -41259,22 +41259,22 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -41288,13 +41288,13 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="O271" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="R271" t="n">
-        <v>0.6976753457479679</v>
+        <v>0.2657810840944639</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -41400,22 +41400,22 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -41429,13 +41429,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>0.2990037196062719</v>
+        <v>0</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -41541,17 +41541,17 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D042</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>麻风病</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -41682,22 +41682,22 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D051</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Zika virus disease</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>寨卡病毒病</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R274" t="n">
-        <v>0</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -41823,22 +41823,22 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>D184</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Accident caused by venomous animals</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>毒性动物伤害</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -41964,22 +41964,22 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -41993,13 +41993,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>490</v>
+        <v>9</v>
       </c>
       <c r="O276" t="n">
-        <v>490</v>
+        <v>9</v>
       </c>
       <c r="R276" t="n">
-        <v>16.27909140078592</v>
+        <v>0.2990037196062719</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -42105,22 +42105,22 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -42246,22 +42246,22 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D168</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>先天性风疹综合征</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -42275,24 +42275,19 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>0.132890542047232</v>
+        <v>0</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>ibge_computed</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42300,30 +42295,26 @@
       </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
@@ -42381,7 +42372,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -42396,17 +42387,17 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -42425,39 +42416,17 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
-        <v>4</v>
-      </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>SRC_BR_SINAN</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr">
-        <is>
-          <t>Meningitis</t>
-        </is>
-      </c>
-      <c r="Y279" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -42465,90 +42434,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>country:BR-DF:national</t>
-        </is>
-      </c>
-      <c r="AD279" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE279" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF279" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG279" t="inlineStr">
-        <is>
-          <t>reported_aggregate</t>
-        </is>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ279" t="inlineStr">
-        <is>
-          <t>BR_SINAN_MENI_current</t>
-        </is>
-      </c>
-      <c r="AK279" t="inlineStr">
-        <is>
-          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
-        </is>
-      </c>
-      <c r="AM279" t="inlineStr">
-        <is>
-          <t>final; provisional</t>
-        </is>
-      </c>
-      <c r="AN279" t="b">
-        <v>1</v>
-      </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ279" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr"/>
       <c r="AT279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
@@ -42578,6 +42485,804 @@
       </c>
       <c r="BB279" t="inlineStr"/>
       <c r="BC279" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D184</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Accident caused by venomous animals</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>毒性动物伤害</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>21</v>
+      </c>
+      <c r="O280" t="n">
+        <v>21</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0.6976753457479679</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr"/>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D191</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Exogenous poisoning</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>外源性中毒</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>490</v>
+      </c>
+      <c r="O281" t="n">
+        <v>490</v>
+      </c>
+      <c r="R281" t="n">
+        <v>16.27909140078592</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr"/>
+      <c r="AT281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr"/>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D201</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Exanthematous diseases</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>出疹性疾病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr"/>
+      <c r="AT282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr"/>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>4</v>
+      </c>
+      <c r="O283" t="n">
+        <v>4</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0.132890542047232</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr"/>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>4</v>
+      </c>
+      <c r="O284" t="n">
+        <v>4</v>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>Meningitis</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>country:BR-DF:national</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>BR_SINAN_MENI_current</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>Brazil SINAN MENI file family spans reported meningitis etiologies and must not be interpreted as bacterial meningitis only.</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN284" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr"/>
+      <c r="BC284" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -42699,7 +43404,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -42709,7 +43414,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -42761,7 +43466,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31771</v>
+        <v>31576</v>
       </c>
     </row>
     <row r="16">

--- a/countries/br-df/2026-2029.xlsx
+++ b/countries/br-df/2026-2029.xlsx
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1267</v>
+        <v>1248</v>
       </c>
       <c r="O25" t="n">
-        <v>1267</v>
+        <v>1248</v>
       </c>
       <c r="R25" t="n">
-        <v>42.09307919346072</v>
+        <v>41.46184911873637</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -8095,13 +8095,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1111</v>
+        <v>1128</v>
       </c>
       <c r="O60" t="n">
-        <v>1111</v>
+        <v>1128</v>
       </c>
       <c r="R60" t="n">
-        <v>36.91034805361868</v>
+        <v>37.47513285731942</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>1252</v>
+        <v>1271</v>
       </c>
       <c r="O95" t="n">
-        <v>1252</v>
+        <v>1271</v>
       </c>
       <c r="R95" t="n">
-        <v>41.5947396607836</v>
+        <v>42.22596973550795</v>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
@@ -16861,13 +16861,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1110</v>
+        <v>1152</v>
       </c>
       <c r="O129" t="n">
-        <v>1110</v>
+        <v>1152</v>
       </c>
       <c r="R129" t="n">
-        <v>36.87712541810686</v>
+        <v>38.27247610960281</v>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
@@ -20803,13 +20803,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>711</v>
+        <v>1168</v>
       </c>
       <c r="O160" t="n">
-        <v>711</v>
+        <v>1168</v>
       </c>
       <c r="R160" t="n">
-        <v>23.62129384889548</v>
+        <v>38.80403827779173</v>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
@@ -24212,17 +24212,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>D188</t>
+          <t>D187</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>Rabies post-exposure prophylaxis</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>职业相关癌症</t>
+          <t>狂犬病暴露后处置</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -24241,13 +24241,13 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="O187" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>38.37214401613823</v>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
@@ -24338,17 +24338,17 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>D189</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Work-related dermatosis</t>
+          <t>Work-related cancer</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>职业性皮肤病</t>
+          <t>职业相关癌症</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -24464,17 +24464,17 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D189</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Work-related dermatosis</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>职业性皮肤病</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -24493,13 +24493,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>32.95685442771353</v>
+        <v>0</v>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
@@ -24590,17 +24590,17 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D191</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Exogenous poisoning</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>外源性中毒</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -24619,18 +24619,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>137</v>
+        <v>992</v>
       </c>
       <c r="O190" t="n">
-        <v>137</v>
+        <v>992</v>
       </c>
       <c r="R190" t="n">
-        <v>4.551501065117694</v>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
+        <v>32.95685442771353</v>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
@@ -24639,7 +24634,7 @@
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
@@ -24647,13 +24642,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -24725,17 +24716,17 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -24754,17 +24745,17 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="O191" t="n">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="R191" t="n">
-        <v>0.6312300747243518</v>
+        <v>4.551501065117694</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -24784,7 +24775,7 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
+          <t>SER_BR_LERD</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -24860,17 +24851,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>D194</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Noise-induced hearing loss</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>噪声性听力损失</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -24889,13 +24880,18 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>0.6312300747243518</v>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
@@ -24904,7 +24900,7 @@
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
@@ -24912,9 +24908,13 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS192" t="inlineStr"/>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -24986,17 +24986,17 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>D195</t>
+          <t>D194</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Pneumoconiosis</t>
+          <t>Noise-induced hearing loss</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>尘肺病</t>
+          <t>噪声性听力损失</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -25112,22 +25112,22 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D195</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Pneumoconiosis</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>尘肺病</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -25141,13 +25141,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.06644527102361598</v>
+        <v>0</v>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
@@ -25238,22 +25238,22 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D201</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Exanthematous diseases</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>出疹性疾病</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -25267,18 +25267,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O195" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R195" t="n">
-        <v>0.5315621681889279</v>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
+        <v>0.06644527102361598</v>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
@@ -25287,7 +25282,7 @@
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
@@ -25295,13 +25290,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -25373,42 +25364,47 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N196" t="n">
-        <v>323</v>
+        <v>16</v>
       </c>
       <c r="O196" t="n">
-        <v>323</v>
+        <v>16</v>
       </c>
       <c r="R196" t="n">
-        <v>10.73091127031398</v>
+        <v>0.5315621681889279</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
@@ -25417,7 +25413,7 @@
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
@@ -25425,9 +25421,13 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS196" t="inlineStr"/>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -25499,22 +25499,22 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -25528,13 +25528,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>6</v>
+        <v>323</v>
       </c>
       <c r="O197" t="n">
-        <v>6</v>
+        <v>323</v>
       </c>
       <c r="R197" t="n">
-        <v>0.1993358130708479</v>
+        <v>10.73091127031398</v>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
@@ -25625,17 +25625,17 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -25654,13 +25654,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O198" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>0.1993358130708479</v>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
@@ -25751,17 +25751,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>D035</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Leptospirosis</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>钩端螺旋体病</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -25877,17 +25877,17 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>D042</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Leprosy</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>麻风病</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -25906,13 +25906,13 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>0.6312300747243518</v>
+        <v>0</v>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
@@ -26003,22 +26003,22 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>D051</t>
+          <t>D042</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Zika virus disease</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>寨卡病毒病</t>
+          <t>麻风病</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -26032,13 +26032,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O201" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R201" t="n">
-        <v>0.03322263551180799</v>
+        <v>0.6312300747243518</v>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
@@ -26129,17 +26129,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D051</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Zika virus disease</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>寨卡病毒病</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -26158,13 +26158,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="O202" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="R202" t="n">
-        <v>1.760799682125823</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
@@ -26255,17 +26255,17 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -26284,13 +26284,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="O203" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="R203" t="n">
-        <v>0.5315621681889279</v>
+        <v>1.760799682125823</v>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
@@ -26381,22 +26381,22 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>D118</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Spotted fever rickettsiosis</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>斑点热立克次体病</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -26410,13 +26410,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>0.5315621681889279</v>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
@@ -26507,17 +26507,17 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D118</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Spotted fever rickettsiosis</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>斑点热立克次体病</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -26633,22 +26633,22 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>D168</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Congenital rubella syndrome</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>先天性风疹综合征</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -26759,22 +26759,22 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D168</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>先天性风疹综合征</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -26885,17 +26885,17 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>D184</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Accident caused by venomous animals</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>毒性动物伤害</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -26914,13 +26914,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>13.38872211125862</v>
+        <v>0</v>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
@@ -27011,17 +27011,17 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>D185</t>
+          <t>D184</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Work accident with biological material</t>
+          <t>Accident caused by venomous animals</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>生物材料职业暴露事故</t>
+          <t>毒性动物伤害</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -27040,13 +27040,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>153</v>
+        <v>403</v>
       </c>
       <c r="O209" t="n">
-        <v>153</v>
+        <v>403</v>
       </c>
       <c r="R209" t="n">
-        <v>5.083063233306622</v>
+        <v>13.38872211125862</v>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
@@ -27137,17 +27137,17 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>D186</t>
+          <t>D185</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Serious work accident</t>
+          <t>Work accident with biological material</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>严重工伤</t>
+          <t>生物材料职业暴露事故</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -27166,13 +27166,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>954</v>
+        <v>153</v>
       </c>
       <c r="O210" t="n">
-        <v>954</v>
+        <v>153</v>
       </c>
       <c r="R210" t="n">
-        <v>31.69439427826482</v>
+        <v>5.083063233306622</v>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
@@ -27263,17 +27263,17 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>D188</t>
+          <t>D186</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>Serious work accident</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>职业相关癌症</t>
+          <t>严重工伤</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -27292,13 +27292,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>31.69439427826482</v>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
@@ -27389,17 +27389,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>D189</t>
+          <t>D187</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Work-related dermatosis</t>
+          <t>Rabies post-exposure prophylaxis</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>职业性皮肤病</t>
+          <t>狂犬病暴露后处置</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -27418,13 +27418,13 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="O212" t="n">
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>45.68112382873598</v>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
@@ -27515,17 +27515,17 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Work-related cancer</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>职业相关癌症</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -27544,13 +27544,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>1149</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>1149</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>38.17280820306738</v>
+        <v>0</v>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
@@ -27641,17 +27641,17 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D189</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Work-related dermatosis</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>职业性皮肤病</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -27670,18 +27670,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>4.186052074487807</v>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
@@ -27690,7 +27685,7 @@
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
@@ -27698,13 +27693,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS214" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+      <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
@@ -27776,17 +27767,17 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D191</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Exogenous poisoning</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>外源性中毒</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -27805,18 +27796,13 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>12</v>
+        <v>1149</v>
       </c>
       <c r="O215" t="n">
-        <v>12</v>
+        <v>1149</v>
       </c>
       <c r="R215" t="n">
-        <v>0.3986716261416959</v>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
+        <v>38.17280820306738</v>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
@@ -27825,7 +27811,7 @@
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
@@ -27833,13 +27819,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -27911,17 +27893,17 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>D194</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Noise-induced hearing loss</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>噪声性听力损失</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -27940,13 +27922,18 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>4.186052074487807</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
@@ -27955,7 +27942,7 @@
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
@@ -27963,9 +27950,13 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS216" t="inlineStr"/>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
       <c r="AT216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
@@ -28037,17 +28028,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>D195</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Pneumoconiosis</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>尘肺病</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -28066,13 +28057,18 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O217" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>0.3986716261416959</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
@@ -28081,7 +28077,7 @@
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
@@ -28089,9 +28085,13 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS217" t="inlineStr"/>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -28163,22 +28163,22 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D194</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Noise-induced hearing loss</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>噪声性听力损失</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -28192,13 +28192,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>0.03322263551180799</v>
+        <v>0</v>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
@@ -28289,17 +28289,17 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D195</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Pneumoconiosis</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>尘肺病</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -28318,18 +28318,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>1.129569607401472</v>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
@@ -28338,7 +28333,7 @@
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
@@ -28346,13 +28341,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+      <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -28424,17 +28415,17 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D201</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Exanthematous diseases</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>出疹性疾病</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -28444,22 +28435,22 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>291</v>
+        <v>1</v>
       </c>
       <c r="O220" t="n">
-        <v>291</v>
+        <v>1</v>
       </c>
       <c r="R220" t="n">
-        <v>9.667786933936124</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
@@ -28550,61 +28541,70 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N221" t="n">
+        <v>34</v>
+      </c>
+      <c r="O221" t="n">
+        <v>34</v>
+      </c>
+      <c r="R221" t="n">
+        <v>1.129569607401472</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
         <v>1</v>
-      </c>
-      <c r="O221" t="n">
-        <v>1</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0.03322263551180799</v>
-      </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO221" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP221" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
-      <c r="AT221" t="n">
-        <v>0</v>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
@@ -28676,22 +28676,22 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -28705,13 +28705,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="O222" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>9.435228485353468</v>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
@@ -28802,17 +28802,17 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>D042</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Leprosy</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>麻风病</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -28831,13 +28831,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O223" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R223" t="n">
-        <v>0.5647848037007358</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
@@ -28928,22 +28928,22 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>D051</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Zika virus disease</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>寨卡病毒病</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -28957,13 +28957,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>0.03322263551180799</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
@@ -29054,22 +29054,22 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D042</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>麻风病</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -29083,13 +29083,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="O225" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="R225" t="n">
-        <v>1.49501859803136</v>
+        <v>0.5647848037007358</v>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
@@ -29180,17 +29180,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D051</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Zika virus disease</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>寨卡病毒病</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -29209,13 +29209,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O226" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R226" t="n">
-        <v>0.5647848037007358</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
@@ -29306,22 +29306,22 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -29335,13 +29335,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O227" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>1.49501859803136</v>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
@@ -29432,17 +29432,17 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D168</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Congenital rubella syndrome</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>先天性风疹综合征</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -29461,13 +29461,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O228" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>0.5647848037007358</v>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
@@ -29558,22 +29558,22 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -29684,22 +29684,22 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>D184</t>
+          <t>D168</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Accident caused by venomous animals</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>毒性动物伤害</t>
+          <t>先天性风疹综合征</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -29713,13 +29713,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>425</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>425</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>14.11962009251839</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
@@ -29810,17 +29810,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>D185</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Work accident with biological material</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>生物材料职业暴露事故</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -29839,13 +29839,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>3.156150373621759</v>
+        <v>0</v>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
@@ -29936,17 +29936,17 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>D186</t>
+          <t>D184</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Serious work accident</t>
+          <t>Accident caused by venomous animals</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>严重工伤</t>
+          <t>毒性动物伤害</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -29965,13 +29965,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>527</v>
+        <v>425</v>
       </c>
       <c r="O232" t="n">
-        <v>527</v>
+        <v>425</v>
       </c>
       <c r="R232" t="n">
-        <v>17.50832891472281</v>
+        <v>14.11962009251839</v>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
@@ -30062,17 +30062,17 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>D188</t>
+          <t>D185</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Work-related cancer</t>
+          <t>Work accident with biological material</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>职业相关癌症</t>
+          <t>生物材料职业暴露事故</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -30091,13 +30091,13 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>3.156150373621759</v>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
@@ -30188,17 +30188,17 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>D189</t>
+          <t>D186</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Work-related dermatosis</t>
+          <t>Serious work accident</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>职业性皮肤病</t>
+          <t>严重工伤</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -30217,13 +30217,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="O234" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>17.50832891472281</v>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
@@ -30314,17 +30314,17 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D187</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Rabies post-exposure prophylaxis</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>狂犬病暴露后处置</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -30343,13 +30343,13 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1244</v>
+        <v>1349</v>
       </c>
       <c r="O235" t="n">
-        <v>1244</v>
+        <v>1349</v>
       </c>
       <c r="R235" t="n">
-        <v>41.32895857668914</v>
+        <v>44.81733530542898</v>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
@@ -30440,17 +30440,17 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>D192</t>
+          <t>D188</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Work-related repetitive strain injury</t>
+          <t>Work-related cancer</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>职业相关重复性劳损</t>
+          <t>职业相关癌症</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -30469,18 +30469,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>3.521599364251647</v>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
@@ -30489,7 +30484,7 @@
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
@@ -30497,13 +30492,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_BR_LERD</t>
-        </is>
-      </c>
+      <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
@@ -30575,17 +30566,17 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>D193</t>
+          <t>D189</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Work-related mental disorder</t>
+          <t>Work-related dermatosis</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>职业相关精神障碍</t>
+          <t>职业性皮肤病</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -30604,18 +30595,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0.4318942616535039</v>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
@@ -30624,7 +30610,7 @@
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
@@ -30632,13 +30618,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_BR_WORK_MENTAL_MENT</t>
-        </is>
-      </c>
+      <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
@@ -30710,17 +30692,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>D194</t>
+          <t>D191</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Noise-induced hearing loss</t>
+          <t>Exogenous poisoning</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>噪声性听力损失</t>
+          <t>外源性中毒</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -30739,13 +30721,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>41.32895857668914</v>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
@@ -30836,17 +30818,17 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>D195</t>
+          <t>D192</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Pneumoconiosis</t>
+          <t>Work-related repetitive strain injury</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>尘肺病</t>
+          <t>职业相关重复性劳损</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -30865,13 +30847,18 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="O239" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>3.521599364251647</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
@@ -30880,7 +30867,7 @@
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
@@ -30888,9 +30875,13 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS239" t="inlineStr"/>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>SER_BR_LERD</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
@@ -30962,22 +30953,22 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D193</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Work-related mental disorder</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>职业相关精神障碍</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -30991,13 +30982,18 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O240" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R240" t="n">
-        <v>0.132890542047232</v>
+        <v>0.4318942616535039</v>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
@@ -31006,7 +31002,7 @@
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
@@ -31014,9 +31010,13 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS240" t="inlineStr"/>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
@@ -31088,17 +31088,17 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D194</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Noise-induced hearing loss</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>噪声性听力损失</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -31117,18 +31117,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>0.6312300747243518</v>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
@@ -31137,7 +31132,7 @@
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
@@ -31145,13 +31140,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+      <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
@@ -31223,42 +31214,42 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D195</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Pneumoconiosis</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>尘肺病</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N242" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>15.21596706440806</v>
+        <v>0</v>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
@@ -31349,42 +31340,42 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D201</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Exanthematous diseases</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>百日咳</t>
+          <t>出疹性疾病</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N243" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O243" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R243" t="n">
-        <v>0.2657810840944639</v>
+        <v>0.132890542047232</v>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
@@ -31475,42 +31466,47 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D235</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Meningitis (all reported etiologies)</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>白喉</t>
+          <t>脑膜炎（全部报告病因）</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>0.6312300747243518</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
@@ -31519,7 +31515,7 @@
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
@@ -31527,9 +31523,13 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS244" t="inlineStr"/>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
@@ -31601,22 +31601,22 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>D042</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Leprosy</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>麻风病</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -31630,13 +31630,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>12.62460149448704</v>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
@@ -31727,22 +31727,22 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>D051</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Zika virus disease</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>寨卡病毒病</t>
+          <t>百日咳</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -31756,13 +31756,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O246" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R246" t="n">
-        <v>0.03322263551180799</v>
+        <v>0.2657810840944639</v>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
@@ -31853,22 +31853,22 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D029</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>白喉</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -31882,13 +31882,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>0.6976753457479679</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
@@ -31979,22 +31979,22 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>D054</t>
+          <t>D042</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Varicella</t>
+          <t>Leprosy</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>水痘</t>
+          <t>麻风病</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -32008,13 +32008,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>0.2990037196062719</v>
+        <v>0</v>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
@@ -32105,22 +32105,22 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D051</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Tetanus</t>
+          <t>Zika virus disease</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>破伤风</t>
+          <t>寨卡病毒病</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -32134,13 +32134,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>0.03322263551180799</v>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
@@ -32231,17 +32231,17 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>D168</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Congenital rubella syndrome</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>先天性风疹综合征</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -32260,13 +32260,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>0.6976753457479679</v>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
@@ -32357,22 +32357,22 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D054</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Varicella</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>水痘</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -32386,13 +32386,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O251" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>0.2990037196062719</v>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
@@ -32483,22 +32483,22 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>D184</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Accident caused by venomous animals</t>
+          <t>Tetanus</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>毒性动物伤害</t>
+          <t>破伤风</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -32512,13 +32512,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0.6976753457479679</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
@@ -32609,22 +32609,22 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>D191</t>
+          <t>D168</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Exogenous poisoning</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>外源性中毒</t>
+          <t>先天性风疹综合征</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -32638,13 +32638,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>16.27909140078592</v>
+        <v>0</v>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
@@ -32735,22 +32735,22 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>D201</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Exanthematous diseases</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>出疹性疾病</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -32861,17 +32861,17 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>D235</t>
+          <t>D184</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Meningitis (all reported etiologies)</t>
+          <t>Accident caused by venomous animals</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>脑膜炎（全部报告病因）</t>
+          <t>毒性动物伤害</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -32890,18 +32890,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O255" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="R255" t="n">
-        <v>0.132890542047232</v>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
+        <v>0.6976753457479679</v>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
@@ -32910,7 +32905,7 @@
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
@@ -32918,13 +32913,9 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
-        </is>
-      </c>
+      <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
@@ -32953,6 +32944,519 @@
       </c>
       <c r="BB255" t="inlineStr"/>
       <c r="BC255" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D187</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Rabies post-exposure prophylaxis</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>狂犬病暴露后处置</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>277</v>
+      </c>
+      <c r="O256" t="n">
+        <v>277</v>
+      </c>
+      <c r="R256" t="n">
+        <v>9.202670036770813</v>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr"/>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D191</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Exogenous poisoning</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>外源性中毒</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>490</v>
+      </c>
+      <c r="O257" t="n">
+        <v>490</v>
+      </c>
+      <c r="R257" t="n">
+        <v>16.27909140078592</v>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
+      <c r="AT257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB257" t="inlineStr"/>
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D201</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Exanthematous diseases</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>出疹性疾病</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
+      <c r="AT258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr"/>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>br-df</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D235</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Meningitis (all reported etiologies)</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>脑膜炎（全部报告病因）</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>4</v>
+      </c>
+      <c r="O259" t="n">
+        <v>4</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0.132890542047232</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_BR_MENINGITIS_ALL_ETIOLOGIES_MENI</t>
+        </is>
+      </c>
+      <c r="AT259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr"/>
+      <c r="BC259" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -33074,7 +33578,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -33084,7 +33588,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -33136,7 +33640,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31576</v>
+        <v>36163</v>
       </c>
     </row>
     <row r="16">
